--- a/output/details/2026-06-02/preprocessed_data.xlsx
+++ b/output/details/2026-06-02/preprocessed_data.xlsx
@@ -15231,25 +15231,25 @@
         <v>46175</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.1197184431253936</v>
+        <v>-0.1275225330707203</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1278182334801705</v>
+        <v>-0.1470408030492557</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1276504321315867</v>
+        <v>-0.1467557911815054</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1134613447001326</v>
+        <v>-0.0002692574914787893</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001694409017627823</v>
+        <v>0.001688394635464929</v>
       </c>
       <c r="G2" t="n">
-        <v>2.011951041241883</v>
+        <v>2.563877298781375</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.426809690474683</v>
+        <v>-0.2648664515241486</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
